--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_02_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_02_18_Cau.xlsx
@@ -957,7 +957,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu từ hành vi không chấp nhận được đã quan sát.</t>
+          <t>Để định nghĩa tiêu chí chất lượng cho một tính năng AI mới, phương pháp khởi đầu phù hợp nhất là chạy thử nghiệm trên các câu trả lời thực tế của mô hình, gom nhóm các lỗi quan sát được lặp lại, và xác lập các khía cạnh đo lường dựa trên mức độ hệ quả của lỗi đối với trải nghiệm sản phẩm.</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hiệu chỉnh cần quan sát chênh lệch trước khi thảo luận.</t>
+          <t>Việc hai người chấm thảo luận trước rồi cùng cho 5/5 câu trả lời đạt chỉ thể hiện sự đồng thuận sau khi đã phối hợp; điều này chưa chứng minh được độ rõ ràng của tiêu chí hay tính đại diện của tập mẫu. Để đánh giá độ tin cậy giữa những người chấm (inter-rater reliability), hai người bắt buộc phải chấm độc lập trước khi đối chiếu và hiệu chuẩn.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_02_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_06_Full_53_Cau/Day_06_Ngan_Hang_Phan_02_18_Cau.xlsx
@@ -674,10 +674,25 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách quyền được làm khỏi độ đúng của dữ liệu và hậu quả.
-Phân tích theo nguyên lý thiết kế: Tách quyền được làm khỏi độ đúng của dữ liệu và hậu quả.</t>
+- 1.0 điểm: Phân loại đúng Lớp vi phạm thẩm quyền hệ thống kèm bằng chứng bot không có quyền nhưng vẫn cấp bằng.
+- 1.0 điểm: Phân loại đúng Lớp rủi ro mạo danh thương hiệu kèm bằng chứng tự ý dùng logo trường trên PDF.
+- 1.0 điểm: Phân loại đúng Lớp sai lệch dữ liệu kèm bằng chứng ghi sai tên khóa học.
+- 1.0 điểm: Chỉ ra dứt khoát Lớp rủi ro chính là Vi phạm Thẩm quyền và giải thích logic nhân quả gốc rễ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Mọi lớp Rủi ro được Bằng chứng Hỗ trợ:
+- Lớp Rủi ro 1: Vi phạm Ranh giới Thẩm quyền / Quyền hạn Hệ thống (System Authority / Scope Boundary Violation):
+  + Bằng chứng hỗ trợ: Trợ giảng AI là một bot giải đáp học tập, hoàn toàn không được cấp thẩm quyền pháp lý hay hành chính để cấp chứng chỉ khóa học, nhưng bot vẫn tự ý tạo và phát hành tài liệu chứng nhận hoàn thành mang tính pháp lý.
+- Lớp Rủi ro 2: Sử dụng Trái phép và Mạo danh Thương hiệu Tổ chức (Unauthorized Branding / Impersonation Risk):
+  + Bằng chứng hỗ trợ: Bot tự tiện nhúng và kết xuất hình ảnh Logo chính thức của nhà trường lên tệp PDF tự tạo mà không qua hệ thống xác thực phôi văn bằng của trường.
+- Lớp Rủi ro 3: Sai lệch Tính chính xác của Dữ liệu / Ảo giác Thông tin (Factual Inaccuracy / Data Fabrication Risk):
+  + Bằng chứng hỗ trợ: Bot ghi sai hoàn toàn tên khóa học trên chứng chỉ cấp cho sinh viên.
+2. Xác định Lớp Rủi ro CHÍNH (Primary Risk Layer):
+- Lớp rủi ro chính: VI PHẠM RANH GIỚI THẨM QUYỀN (System Authority Violation).
+- Biện minh: Đây là gốc rễ của sự cố. Nếu bot tuân thủ đúng thẩm quyền (nhận thức rõ mình không có quyền cấp chứng chỉ và từ chối ngay lập tức), thì lỗi mạo danh logo trường và lỗi ghi sai tên khóa học sẽ hoàn toàn KHÔNG CÓ CƠ HỘI PHÁT SINH. Hành vi tự ý ban hành văn bằng vượt quyền là vi phạm an ninh nghiêm trọng nhất trong hệ thống AI.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong mô hình phân cấp rủi ro AI, rủi ro Thẩm quyền (Authority Risk) luôn là lớp rủi ro gốc chi phối các rủi ro dữ liệu (Factual Risk). Một AI bị ảo giác dữ liệu có thể gây khó chịu, nhưng một AI hành động vượt thẩm quyền pháp lý (cấp bằng giả mạo thương hiệu) sẽ đẩy tổ chức vào nguy cơ khủng hoảng pháp lý và uy tín học thuật nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI Risk Management Framework (AI RMF 1.0) &amp; OWASP Top 10 for LLM: LLM08 Excessive Agency (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
@@ -708,10 +723,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Viết hành vi mà người chấm có thể đưa dữ liệu vào và quan sát.
-Phân tích theo nguyên lý thiết kế: Viết hành vi mà người chấm có thể đưa dữ liệu vào và quan sát.</t>
+- 1.0 điểm: Thiết lập điều kiện kích hoạt cụ thể bằng câu hỏi ngoài tài liệu nguồn của khóa học.
+- 1.0 điểm: Xác định đúng lớp rủi ro là Out-of-Domain Grounding Risk.
+- 1.0 điểm: Mô tả chính xác hành vi người học nhìn thấy: từ chối trung thực, nêu rõ giới hạn tài liệu.
+- 1.0 điểm: Nêu rõ hành động tiếp theo của người học và nguyên tắc thiết kế trung thực (Strict Grounding/Graceful Refusal).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Đặc tả Kịch bản Rủi ro Hành vi (Risk Scenario Behavior Specification):
+1. Điều kiện Kích hoạt (Trigger Condition):
+- Người học gửi một câu hỏi về một khái niệm nằm ngoài giáo trình (ví dụ: 'Hãy giải thích thuật toán Q-learning trong học tăng cường' trong khi môn học hiện tại chỉ dạy về Mạng nơ-ron tích chập CNN).
+2. Lớp Rủi ro Áp dụng (Applicable Risk Layer):
+- Lớp rủi ro: Thoát khỏi Nguồn Tri thức Chuẩn mực / Ảo giác Ngoài phạm vi (Out-of-Domain Knowledge Boundary / Grounding Integrity Risk).
+3. Hành vi Người học Nhìn thấy trên Màn hình (Observable Learner-Facing Behavior):
+- Trợ giảng AI KHÔNG được tự ý tìm kiếm tri thức ngoài để trả lời bừa.
+- Màn hình hiển thị thông điệp trung thực và lịch sự: 'Khái niệm "Q-learning" hiện không nằm trong nội dung tài liệu của khóa học này. Trợ giảng chỉ được hỗ trợ giải đáp các chủ đề thuộc phạm vi giáo trình Mạng nơ-ron tích chập (CNN). Bạn có muốn đặt câu hỏi về các bài học trong tuần này không?'.
+4. Hành động Tiếp theo của Người học (Learner Next Action):
+- Người học nhận thức rõ ranh giới kiến thức của khóa học, bấm nút gợi ý 'Xem lại danh sách chủ đề khóa học' hoặc nhập lại câu hỏi khác liên quan đến bài tập CNN hiện tại.
+5. Nguyên tắc được Áp dụng (Underlying Principle):
+- Nguyên tắc Trả lời Trung thực Dựa trên Nguồn (Strict Grounding &amp; Knowing What It Doesn't Know / Graceful Refusal): Thà từ chối trung thực còn hơn trả lời sai lệch hoặc đưa kiến thức ngoài gây hoang mang cho người học.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một đặc tả kịch bản rủi ro chuẩn mực phải cung cấp đầy đủ dữ kiện để kiểm toán viên có thể tái hiện độc lập: Nhập câu hỏi kích hoạt -&gt; Quan sát hành vi từ chối lịch sự trên màn hình -&gt; Kiểm tra hành động chuyển hướng tiếp theo. Đây là tiêu chuẩn kiểm định an toàn của mọi gia sư AI học đường.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Design for Robustness &amp; Pedagogical Safeguards for AI Tutors (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -788,10 +820,28 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng để dạng đầu ra bị lẫn với thay đổi ở mô hình hoặc nội dung.
-Phân tích theo nguyên lý thiết kế: Đừng để dạng đầu ra bị lẫn với thay đổi ở mô hình hoặc nội dung.</t>
+- 1.0 điểm: Mô tả chi tiết 2 biến thể đối chiếu rõ ràng: Biến thể A (gạch đầu dòng) và Biến thể B (đoạn văn liền).
+- 1.0 điểm: Xác định chặt chẽ các yếu tố giữ nguyên cố định (nội dung tri thức, phiên bản model, nhiệt độ, giao diện khung).
+- 1.0 điểm: Đưa ra tín hiệu đo lường so sánh khách quan (thời gian duyệt tính bằng giây, tỷ lệ sửa từ).
+- 1.0 điểm: Nêu rõ phương pháp ghi chép lý do loại bỏ có căn cứ số liệu thực nghiệm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Thử nghiệm So sánh Biến thể Thiết kế Sản phẩm (Product Design Variant Test):
+1. Mô tả Hai biến thể Giao diện Đầu ra (Two Design Variants):
+- Biến thể A (Bullet-point Variant): Câu trả lời của AI được định dạng cấu trúc gồm 3–4 gạch đầu dòng ngắn gọn, mỗi gạch đầu dòng bắt đầu bằng một từ khóa in đậm (Keyword Highlight).
+- Biến thể B (Paragraph Variant): Câu trả lời của AI được định dạng thành một đoạn văn liền mạch (Prose Narrative) dài từ 4–5 câu thông thường.
+2. Phần BẮT BUỘC PHẢI GIỮ NGUYÊN TUYỆT ĐỐI (Controlled Invariants):
+- Nội dung tri thức và Dữ kiện sự thật (Factual Information): Giữ nguyên 100% cùng một bộ dữ liệu câu hỏi của sinh viên và cùng các luận điểm giải thích kỹ thuật.
+- Mô hình AI và Nhiệt độ suy luận (Model &amp; Temperature): Cùng sử dụng một phiên bản model snapshot duy nhất với `temperature = 0`.
+- Môi trường hiển thị: Cùng kích thước phông chữ, cùng độ rộng khung chat và cùng bối cảnh thời gian kiểm thử.
+3. Tín hiệu So sánh Khách quan (Comparison Signals):
+- Tín hiệu 1 (Thời gian xem xét - Time to Review): Đo lường bằng đồng hồ bấm giờ (timestamp) từ lúc câu trả lời hiển thị đến khi TA bấm nút 'Duyệt gửi' hoặc 'Chỉnh sửa'.
+- Tín hiệu 2 (Tỷ lệ chỉnh sửa - Edit Rate): Tỷ lệ phần trăm từ ngữ mà TA phải sửa lại trước khi gửi sinh viên.
+4. Cách ghi nhận Lý do Loại bỏ một Biến thể (Documenting Rejection Rationale):
+Lập bảng nhật ký thử nghiệm ghi rõ: 'Loại bỏ Biến thể B vì thời gian đọc trung bình của TA lâu hơn 38% (42 giây so với 26 giây của Biến thể A) và 80% TA phản hồi rằng đoạn văn dài khiến họ khó quét nhanh các công thức toán học trọng tâm'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiểm thử biến thể thiết kế sản phẩm (Variant Testing), việc cô lập biến số hình thức (Form factor) trong khi giữ cố định 100% nội dung và mô hình là nguyên tắc vàng. Nếu để biến thể dạng đoạn văn có nội dung khác với dạng gạch đầu dòng, kết quả thử nghiệm tốc độ đọc sẽ bị sai lệch hoàn toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - A/B Testing Guidelines for UX &amp; Controlled Experimentation in Design (https://www.nngroup.com/articles/)</t>
         </is>
       </c>
     </row>
@@ -874,10 +924,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dữ liệu từ đầu vào của người dùng tới kết quả họ nhìn thấy.
-Phân tích theo nguyên lý thiết kế: Theo dữ liệu từ đầu vào của người dùng tới kết quả họ nhìn thấy.</t>
+- 1.0 điểm: Đánh giá chính xác bản mẫu không đạt do máy chủ trả JSON cố định, đứt gãy luồng dữ liệu thực.
+- 1.0 điểm: Đề xuất bản sửa tối thiểu khả thi: đóng gói sổ tay thành API endpoint (FastAPI) nhận input thực từ UI.
+- 1.0 điểm: Mô tả đường truyền dữ liệu khép kín từ lúc upload CV -&gt; model suy luận -&gt; kết quả động trên UI.
+- 1.0 điểm: Liệt kê đầy đủ dấu vết kiểm toán cần lưu giữ (file hash, log suy luận thời gian thực, response trace).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Bản mẫu Hiện tại:
+- KẾT LUẬN: BẢN MẪU HOÀN TOÀN KHÔNG ĐẠT (FAIL / INVALID DEMO).
+- Lý do: Đây là một bản mô phỏng giả lập cứng (Hardcoded Mock / Facade). Máy chủ luôn trả về một JSON cố định bất kể ứng viên tải lên CV gì. Mặc dù nhóm có một sổ tay Jupyter chạy mô hình AI thật, nhưng luồng dữ liệu từ giao diện của người dùng bị đứt gãy, không hề kết nối tới lõi AI. Kết quả hiển thị trên màn hình không phản ánh dữ liệu đầu vào thực tế của người dùng.
+2. Bản sửa Tối thiểu để Đạt chuẩn Tích hợp Thực (Minimum Integration Fix):
+- Đóng gói logic từ sổ tay Jupyter thành một API Endpoint nội bộ đơn giản (sử dụng FastAPI hoặc Flask, ví dụ: `POST /api/score-resume`).
+- Thay thế phản hồi JSON cố định trên server bằng lời gọi trực tiếp tới API endpoint vừa tạo: Đọc văn bản CV mà người dùng vừa tải lên -&gt; Truyền vào hàm suy luận mô hình AI -&gt; Nhận kết quả điểm số động tương ứng với đúng CV đó -&gt; Trả về giao diện hiển thị.
+3. Dấu vết Bắt buộc phải Lưu giữ để Kiểm toán (Audit Trace Artifacts):
+- `request_payload_trace`: Toàn bộ văn bản trích xuất từ CV của ứng viên kèm mã `file_hash`.
+- `model_execution_log`: Log thời gian thực thi của mô hình, token sử dụng, và ID của phiên suy luận.
+- `response_output_trace`: JSON điểm số thực tế do mô hình sinh ra tương ứng với đúng `request_payload_trace` đó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một bản mẫu sản phẩm AI chỉ được công nhận là hợp lệ khi luồng dữ liệu khép kín (End-to-End Data Lineage) kết nối từ đầu vào của người dùng đến lõi suy luận của AI và phản hồi lên màn hình. Một giao diện trả về JSON cố định tách rời khỏi sổ tay AI chỉ là một hình thức đánh lừa nhận thức (Demo theater), không có giá trị kiểm chứng kỹ thuật.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Teamwork Integrity Mandate - Prohibition of Facade Implementations &amp; Real AI Core Integration Standards (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -908,10 +973,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi nhóm lỗi cần tên gọi và hệ quả riêng.
-Phân tích theo nguyên lý thiết kế: Mỗi nhóm lỗi cần tên gọi và hệ quả riêng.</t>
+- 1.0 điểm: Suy ra chính xác Khía cạnh 1: Độ chuẩn xác trích dẫn nguồn (từ 4 câu trích sai trang) kèm hệ quả mất niềm tin.
+- 1.0 điểm: Suy ra chính xác Khía cạnh 2: Tính cô đọng/mật độ thông tin (từ 3 câu dài gấp 3) kèm hệ quả quá tải nhận thức/tốn token.
+- 1.0 điểm: Suy ra chính xác Khía cạnh 3: Nhận thức ranh giới/chống đoán bừa (từ 2 câu đoán khi thiếu đề) kèm hệ quả sư phạm.
+- 1.0 điểm: Tách bạch rõ rệt 3 nhóm lỗi thành 3 chiều đo lường chất lượng trực giao (orthogonal quality dimensions).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Suy ra Ba Khía cạnh Chất lượng Riêng biệt và Hệ quả Sản phẩm Tương ứng:
+1. Khía cạnh 1: Độ chuẩn xác của Trích dẫn Nguồn gốc (Citation &amp; Attribution Accuracy)
+- Dữ kiện hỗ trợ: 4/12 câu trả lời trích dẫn sai số trang của tài liệu.
+- Hệ quả đối với sản phẩm (Product Impact): Phá hủy hoàn toàn niềm tin của sinh viên và trợ giảng. Sinh viên mất thời gian lật tìm tài liệu ở trang sai và cho rằng hệ thống AI bị ảo giác, làm tăng gấp đôi khối lượng công việc cho trợ giảng khi phải đối chiếu thủ công lại từ đầu.
+2. Khía cạnh 2: Tính Cô đọng và Tối ưu Hóa Nhận thức (Conciseness &amp; Information Density)
+- Dữ kiện hỗ trợ: 3/12 câu trả lời có độ dài gấp 3 lần mức cần thiết.
+- Hệ quả đối với sản phẩm (Product Impact): Gây quá tải nhận thức cho người học, làm giảm tốc độ rà soát của trợ giảng, tăng chi phí tiêu tốn token của hệ thống và khiến sinh viên nản lòng không muốn đọc hết câu trả lời.
+3. Khía cạnh 3: Tự Nhận thức Ranh giới Tri thức và Kiểm soát Ảo giác (Knowledge Boundary Awareness &amp; Non-Fabrication)
+- Dữ kiện hỗ trợ: 2/12 câu trả lời tự ý suy đoán bừa khi đề bài bị thiếu thông tin.
+- Hệ quả đối với sản phẩm (Product Impact): Rủi ro sư phạm nghiêm trọng. Việc AI suy đoán sai đề bài sẽ hướng dẫn sai kiến thức cho sinh viên, dẫn đến kết quả làm bài tập sai và gây ra những tranh chấp học thuật tiêu cực trong khóa học.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quá trình suy diễn khía cạnh chất lượng từ đầu ra (Output-Led Quality Derivation) đòi hỏi đặt tên chính xác cho từng nhóm lỗi và phân tích tác động trực tiếp của nó lên trải nghiệm người dùng và chi phí vận hành. Một hệ thống tốt phải đo lường độc lập cả 3 khía cạnh: Trích dẫn đúng, Độ dài vừa đủ, và Từ chối khi thiếu dữ kiện.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Evaluating AI Output Quality &amp; Educational AI System Quality Dimensions (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1034,10 +1114,28 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một ngưỡng số đơn lẻ có thể bỏ sót chất lượng nội dung.
-Phân tích theo nguyên lý thiết kế: Một ngưỡng số đơn lẻ có thể bỏ sót chất lượng nội dung.</t>
+- 1.0 điểm: Xây dựng quy tắc Đạt/Không đạt kết hợp giữa khoảng độ dài [50-100 từ] và tiêu chí nội dung/hành động tiếp theo.
+- 1.0 điểm: Đánh giá chính xác cả 3 ca: A (Đạt), B (Không đạt do dài/lặp), C (Không đạt do thiếu hành động).
+- 1.0 điểm: Cho phép dung sai ngữ nghĩa đối với các cách diễn đạt khác nhau.
+- 1.0 điểm: Chỉ ra chính xác 1 trường hợp ranh giới chưa giải quyết (ví dụ: 101 từ do thuật ngữ chuyên ngành).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quy tắc Đạt / Không đạt Có thể Chấm điểm (Operationalized Scoring Rule):
+- Quy tắc ĐẠT (Pass): Câu trả lời phải thỏa mãn ĐỒNG THỜI 3 điều kiện:
+  + Điều kiện Độ dài: Số lượng từ nằm trong khoảng chuẩn `[50, 100]` từ.
+  + Điều kiện Nội dung Cốt lõi: Chứa đầy đủ các ý chính giải thích bản chất khái niệm được hỏi mà không bị lặp từ/lặp ý rườm rà.
+  + Điều kiện Hành động Hướng dẫn: Chứa ít nhất một chỉ dẫn hành động tiếp theo cụ thể cho người học (Next Action Step, ví dụ: 'Hãy mở file bài tập 2 và chạy thử lệnh...').
+- Áp dụng trên 3 ví dụ cho trước:
+  + Câu trả lời A (70 từ, đủ ý, có hành động tiếp theo): ĐẠT (Pass).
+  + Câu trả lời B (130 từ, lặp ý): KHÔNG ĐẠT (Fail - vi phạm trần độ dài &gt;100 từ và lỗi lặp ý).
+  + Câu trả lời C (85 từ, thiếu hành động tiếp theo): KHÔNG ĐẠT (Fail - vi phạm điều kiện thiếu chỉ dẫn hành động tiếp theo).
+2. Chấp nhận Cách diễn đạt Khác nhau (Semantic Equivalence Tolerance):
+Chấp nhận mọi phong cách hành văn (viết gạch đầu dòng hoặc viết đoạn văn tự nhiên) miễn là đảm bảo số từ nằm trong khoảng 50–100 từ và truyền tải đầy đủ ngữ nghĩa của ý chính và hành động tiếp theo, không bắt buộc phải giống từng chữ với câu mẫu.
+3. Một Trường hợp Ranh giới Chưa giải quyết (Unresolved Boundary Case):
+Trường hợp câu trả lời có độ dài đúng 101 từ (vượt trần đúng 1 từ duy nhất do chứa một thuật ngữ kỹ thuật tiếng Anh dài), nhưng nội dung xuất sắc và hành động tiếp theo rất rõ ràng. Cần xem xét có nên áp dụng khoảng dung sai (Tolerance margin ±5%) hay giữ cứng ngưỡng 100 từ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Vận hành hóa tiêu chí đánh giá (Criterion Operationalization) yêu cầu chuyển hóa một khái niệm trừu tượng ('đúng độ dài') thành một quy tắc logic đa biến có thể chấm điểm tự động. Việc chỉ đếm số từ đơn thuần sẽ bỏ sót chất lượng nội dung (như câu C), do đó quy tắc phải kết hợp giữa khoảng số từ cho phép và các yếu tố cấu trúc nội dung bắt buộc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Educational Assessment Rubric Design &amp; Operationalizing Quality Metrics in Natural Language Processing (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -1068,10 +1166,22 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách câu chữ bề mặt khỏi bằng chứng về nghĩa.
-Phân tích theo nguyên lý thiết kế: Tách câu chữ bề mặt khỏi bằng chứng về nghĩa.</t>
+- 1.0 điểm: Chỉ ra chính xác sai lầm của tiêu chí cũ: ép khớp câu chữ bề mặt (Exact Match) làm đánh trượt sai.
+- 1.0 điểm: Sửa lại tiêu chí mới dựa trên tính tương đương ngữ nghĩa sự kiện và nguồn trích dẫn.
+- 1.0 điểm: Nêu rõ việc chấp nhận từ đồng nghĩa và cách diễn đạt linh hoạt.
+- 1.0 điểm: Khẳng định điều phải giữ nghiêm ngặt: độ chính xác tuyệt đối của các thực thể sự kiện và số liệu cứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa phần tiêu chí gây đánh trượt sai (Fixing the Flawed Evaluation Criterion):
+- Tiêu chí CŨ (Gây lỗi đánh trượt sai): 'Đạt nếu câu chữ giống câu trả lời mẫu' (Surface Exact Match / String Equality).
+- Tiêu chí MỚI ĐÃ SỬA (Semantic &amp; Factual Alignment): 'ĐẠT nếu câu trả lời đáp ứng đầy đủ hai điều kiện:
+  (1) Tương đồng về Ngữ nghĩa và Sự kiện (Semantic &amp; Factual Equivalence): Chứa đầy đủ các thực thể và mối quan hệ sự kiện cốt lõi được nêu trong câu trả lời mẫu, chấp nhận việc sử dụng các từ đồng nghĩa, đảo cấu trúc ngữ pháp, hoặc cách diễn đạt tương đương.
+  (2) Khớp nối Nguồn dẫn chứng (Source Grounding): Dẫn đúng nguồn tài liệu chính thức (tên tài liệu, chương/mục) được quy định trong tài liệu mẫu'.
+2. Điều BẮT BUỘC PHẢI GIỮ NGHIÊM NGẶT (Strict Non-Negotiable Invariants):
+- Phải giữ nghiêm ngặt Tính Đúng đắn của Dữ kiện Lịch sử / Sự thật Số liệu (Factual Truth &amp; Entity Integrity): Tuyệt đối không cho phép dung sai đối với các con số cụ thể (ví dụ: ngày tháng, số liệu phần trăm, tên thuật ngữ chuẩn, mã hàm). Nếu câu mẫu ghi 'học phí 5 triệu' mà câu trả lời ghi 'học phí 6 triệu', câu đó bắt buộc phải bị đánh trượt ngay lập tức dù câu chữ có mượt mà đến đâu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong đánh giá mô hình ngôn ngữ lớn (LLM Evaluation), việc áp dụng tiêu chí so khớp chuỗi ký tự bề mặt (Exact String Match) là một phản hoa tiêu nguy hiểm, dẫn đến tỷ lệ False Negative (đánh trượt oan các câu trả lời đúng nghĩa) rất cao. Cần chuyển đổi sang đánh giá dựa trên sự tương đồng ngữ nghĩa sự kiện (Factual Consistency), đồng thời giữ kỷ luật nghiêm ngặt về các thực thể dữ liệu cứng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RAG Triad of Metrics (TruLens) - Groundedness and Context Relevance vs. Surface Metrics (https://www.trulens.org/trulens_eval/core_concepts_rag_triad/)</t>
         </is>
       </c>
     </row>
@@ -1152,10 +1262,28 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm đúng từ khiến hai người dùng hai quy tắc ngầm khác nhau.
-Phân tích theo nguyên lý thiết kế: Tìm đúng từ khiến hai người dùng hai quy tắc ngầm khác nhau.</t>
+- 1.0 điểm: Chẩn đoán đúng từ ngữ gây lỗi là 'ngắn gọn' và chỉ rõ 2 quy tắc ngầm mâu thuẫn của người chấm A và B.
+- 1.0 điểm: Sửa lại rubric rõ ràng kết hợp độ dài có biên độ hợp lý [80-120 từ] và mật độ thông tin không lặp ý.
+- 1.0 điểm: Đảm bảo bản sửa giải quyết dứt điểm xung đột trên câu 110 từ.
+- 1.0 điểm: Đề xuất phương pháp kiểm tra lại độ nhất quán độc lập bằng hệ số Cohen's Kappa trên tập mẫu mù.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán Nguyên nhân Gốc rễ của Sự Bất đồng (Diagnostic of Inter-rater Disagreement):
+- Từ ngữ mơ hồ gây ra bất đồng: Cụm từ 'ngắn gọn'.
+- Phân tích cơ chế lỗi: Tiêu chí 'ngắn gọn' là một khái niệm mang tính định tính chủ quan cao, không có định nghĩa thao tác (operational definition). Người chấm A diễn giải ngầm 'ngắn gọn' là 'không chứa thông tin thừa thãi/không lặp ý' (Cognitive Conciseness). Ngược lại, Người chấm B diễn giải ngầm 'ngắn gọn' là 'số từ bắt buộc phải dưới một con số cơ học cụ thể, ví dụ &lt;= 100 từ' (Arbitrary Character Cap). Vì hai người áp dụng hai mô hình phán đoán ngầm hoàn toàn trái ngược nhau, kết quả chấm điểm trên cùng một câu trả lời 110 từ bị xung đột nghiêm trọng.
+2. Viết lại Bản sửa Tiêu chuẩn hóa (Calibrated Rubric Revision):
+- Tiêu chí sửa đổi: Thay thế từ 'ngắn gọn' bằng quy tắc định lượng kết hợp định tính rõ ràng:
+  'Tiêu chí Độ dài và Tính súc tích (Đạt khi thỏa mãn cả 2 điều kiện):
+   (1) Độ dài cơ học: Tổng số từ nằm trong khoảng từ 80 đến 120 từ.
+   (2) Mật độ thông tin: Mỗi câu văn phải truyền tải một dữ kiện độc lập, không có câu nào lặp lại ý của câu trước'.
+   -&gt; Với quy chuẩn này, câu trả lời 110 từ không lặp ý sẽ được cả hai người chấm đồng thuận cho ĐẠT (Pass).
+3. Quy trình Kiểm tra lại Độ nhất quán (Inter-rater Reliability Verification):
+- Chọn ra một tập mẫu mù gồm 20 câu trả lời có độ dài và phong cách đa dạng.
+- Yêu cầu cả Người chấm A và Người chấm B chấm điểm độc lập trên bộ mẫu này theo rubric mới.
+- Tính toán hệ số nhất quán Cohen's Kappa (hoặc Fleiss' Kappa): Nếu điểm số đồng thuận đạt `Kappa &gt;= 0.85`, rubric được coi là đã chuẩn hóa thành công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Inter-rater Reliability (độ tin cậy liên người chấm) là thước đo chất lượng của một Rubric. Các từ ngữ mơ hồ như 'ngắn gọn', 'dễ hiểu', 'hay' là mầm mống phá vỡ tính nhất quán. Chuẩn hóa rubric bằng ngưỡng định lượng có biên độ và đo lường lại bằng chỉ số Cohen's Kappa là phương pháp khoa học chuẩn mực để hiệu chuẩn người chấm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Klaus Krippendorff - Content Analysis: An Introduction to Its Methodology (Inter-coder Reliability &amp; Cohen's Kappa) (https://methods.sagepub.com/book/content-analysis-4e)</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1414,29 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đếm các điều kiện khác nhau, không chỉ đếm số dòng.
-Phân tích theo nguyên lý thiết kế: Đếm các điều kiện khác nhau, không chỉ đếm số dòng.</t>
+- 1.0 điểm: Chỉ ra lỗi thiếu độ phủ trên các nhóm rủi ro quan trọng (mơ hồ, thẩm quyền, gây hại).
+- 1.0 điểm: Chỉ ra lỗi trùng lặp dữ liệu nghiêm trọng (12 ca lấy từ cùng 1 đoạn chat gây rò rỉ và thiên kiến).
+- 1.0 điểm: Nhận diện hiện tượng bộ test quá dễ (100% pass, ceiling effect không phân loại được).
+- 1.0 điểm: Đề xuất phương án sửa đổi cụ thể: loại bớt ca trùng lặp, bổ sung đầy đủ các ca thẩm quyền/mơ hồ/gây hại.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kiểm tra Các Lỗi Nghiêm trọng trong Bộ Mẫu Hiện tại (Golden Set Audit):
+- Lỗi 1 (Mất cân đối nghiêm trọng về độ phủ - Zero Coverage on Critical Risk Categories):
+  + Bộ dữ liệu hoàn toàn thiếu vắng 3 nhóm tình huống sống còn: Tình huống Mơ hồ (Ambiguous queries), Tình huống Thẩm quyền hệ thống (System Authority / Privilege queries), và Tình huống Gây hại chuyên ngành (Domain-specific Harm / Safety violations). Một bộ test chỉ có ca dễ và ca nguồn sự thật sẽ tạo ra cảm giác an tâm giả tạo.
+- Lỗi 2 (Nhiễm độc dữ liệu do trùng lặp nguồn - Data Leakage / Duplication):
+  + Có tới 12/22 tình huống được sao chép từ cùng một cuộc trò chuyện duy nhất. Điều này vi phạm tính độc lập thống kê (Statistical Independence), khiến mô hình bị overfit vào văn phong của một người dùng duy nhất.
+- Lỗi 3 (Thiếu tính phân loại - Ceiling Effect / Non-discriminative Test):
+  + Tỷ lệ đạt 100% (22/22 đều pass) chứng minh bộ test quá dễ, không có khả năng phát hiện lỗi biên của hệ thống.
+2. Đề xuất Cách sửa Tối thiểu (Minimum Golden Set Remediation):
+- Tái cấu trúc bộ mẫu thành 30 tình huống đa dạng và độc lập:
+  + Lọc bỏ 10 tình huống trùng lặp từ cùng một cuộc trò chuyện (chỉ giữ lại 2 tình huống đại diện).
+  + Bổ sung 5 tình huống Mơ hồ (người dùng hỏi thiếu dữ kiện, đòi hỏi bot phải hỏi lại).
+  + Bổ sung 5 tình huống Thẩm quyền (người dùng yêu cầu bot cấp chứng chỉ hoặc đổi điểm thi, bot phải từ chối).
+  + Bổ sung 5 tình huống Gây hại sư phạm (yêu cầu bot giải hộ toàn bộ bài thi trắc nghiệm để gian lận).
+  + Giữ lại 8 tình huống nguồn sự thật và 5 tình huống thông thường đến từ các người dùng khác nhau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một Golden Evaluation Set (Bộ dữ liệu mẫu vàng) có giá trị phải phản ánh đầy đủ phổ rủi ro thực tế của sản phẩm. Một bộ test mà 100% ca kiểm thử đều pass, sao chép từ một đoạn chat và thiếu hoàn toàn các ca thử thách thẩm quyền là một bộ test vô dụng, không có giá trị bảo đảm chất lượng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Testing &amp; Evaluation Datasets &amp; Best Practices for Golden Test Set Construction in LLMs (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
